--- a/USAID_US_Embassy_Lebanon.xlsx
+++ b/USAID_US_Embassy_Lebanon.xlsx
@@ -413,8 +413,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E270"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:E281"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
     <col width="55" customWidth="1" min="2" max="2"/>
@@ -10920,6 +10920,381 @@
         </is>
       </c>
     </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>U.S. EMBASSY BEIRUT OPERATIONS</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>https://lb.usembassy.gov/u-s-embassy-beirut-operations/</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>Beirut, October 28, 2026
+U.S. Embassy Beirut remains open for business, including limited routine American citizen and visa services.
+U.S. citizens traveling or living in the Middle East should enroll in the U.S. Department of State’s Smart Traveler Enrollment Program. STEP enrollment provides the latest security updates and makes it easier for the U.S. embassy in the location where a STEP enrollee is traveling to contact her/him in an emergency. To sign up, visit: https://mytravel.state.gov/s/step.
+Stay connected with the Embassy by visiting our English (https://lb.usembassy.gov/) and Arabic (https://lb.usembassy.gov/ar/homepage-ar/) language websites and via
+Facebook (https://www.facebook.com/USEmbassyBeirut/),
+Instagram (https://www.instagram.com/usembassybeirut/),
+X (https://x.com/usembassybeirut)
+YouTube (https://www.youtube.com/@usinbeirut), and
+WhatsApp Channel (https://whatsapp.com/channel/0029VaUiCFg6hENiACjfs51q)</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:10:03.463451+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Ministry of Culture and U.S. Embassy Celebrate Mussaylha Fort Project</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>https://lb.usembassy.gov/ministry-of-culture-and-u-s-embassy-celebrate-mussaylha-fort-project/</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>Beirut, October 16, 2026 – In the presence of Minister of Culture Dr. Ghassan Salamé, U.S. Ambassador to Beirut Michel Issa, and a gathering of local officials and cultural heritage leaders, the Lebanese Ministry of Culture and U.S. Embassy Beirut celebrated the completion of the preservation and restoration work at the Mussaylha Archaeological Site. The four-year project was made possible through a grant of $210,000 from the U.S. Ambassadors Fund for Cultural Preservation (AFCP). The project restored and reinforced the historic Mussaylha Fort, preserved its architectural character, and improved the road to the site as well as safeguarded local traditions, including restoring the operation of the Fort’s historic mill and providing a natural water reservoir and workshops dedicated to training local farmers on the best and most environmentally friendly agricultural tools and practices. A documentary of the project titled “Mussaylha Fort Through History” is available on YouTube .
+During the celebration, Minister of Culture Dr. Ghassan Salamé stated: “Preserving cultural heritage protects the memory and identity of a place while creating opportunities for its future. The Mussaylha project brings these aims together: alongside conserving the fort, it reactivated its historic mill, revived traditional crops, and supported local farmers in adopting sustainable practices. I thank the U.S. Ambassadors Fund for Cultural Preservation, the Directorate General of Antiquities, Jouzour Loubnan, the Municipality of Hamat, and the local community for making this work possible.”
+In his remarks, Ambassador Issa stated “The Mussaylha project reflects the strength and depth of U.S.-Lebanon ties and over two hundred years of friendship. The United States is committed to supporting Lebanon’s sovereignty, security, and economic future. But we also believe that Lebanon’s cultural heritage is an important part of its identity. Preserving that heritage means protecting Lebanon’s history for future generations.”
+Ambassador Issa also announced that starting this year the U.S. Government will invest $436,827 USD to preserve a Roman-era archaeological site in Chim and revive its centuries-old olive oil tradition. The Embassy will partner with the Ministry of Culture and Beit el Baraka on the new project.
+The Ambassadors Fund for Cultural Preservation, known as AFCP, is among the U.S. Government’s most significant cultural initiatives abroad. Over the past 25 years, the United States has partnered with Lebanon to support 25 AFCP projects totaling over USD $2 million to protect archaeological sites across the country and preserve the shared human heritage that defines the region’s identity, from the Beiteddine Palace to the Mar Bichay Hermitage in Qadisha Valley to the Saida Sea Castle.
+Ambassadors Fund for Cultural Preservation: The U.S. Congress established the Ambassadors Fund for Cultural Preservation in 2001 to preserve a wide range of cultural heritage, including historic buildings, archaeological sites, ethnographic objects, paintings, manuscripts, and indigenous languages and other forms of traditional cultural expression. AFCP projects may support post-disaster and post-conflict recovery, create economic opportunities, and build mutual understanding. AFCP projects typically involve expert local partners and promote the use of traditional materials and methods. The AFCP program reflects American values and demonstrates U.S. friendship. Since its establishment in 2001, the United States has supported over 1,250 AFCP preservation projects in 130 countries.</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:10:10.698215+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Ambassador Issa on the Passing of U.S. Ambassador Battle</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>https://lb.usembassy.gov/ambassador-issa-on-the-passing-of-u-s-ambassador-battle/</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>“On behalf of U.S. Embassy Beirut, I extend our deepest condolences to the family and friends of former U.S. Ambassador to Lebanon, Vincent M. Battle, on his passing. Ambassador Battle, who served with distinction as both Ambassador (2001-2004) and Deputy Chief of Mission (1991-1994) at U.S. Embassy Beirut, had an abiding love for Lebanon and the Lebanese people, leading him to make his home here at the conclusion of his 30+ year diplomatic career. He is remembered by the Embassy community for his deep respect for local staff, enduring love of Lebanese history, culture, and the country’s diverse natural landscapes, and his tireless commitment to strengthening cultural and people-to-people ties between Americans and Lebanese. He will be missed.” – Ambassador Michel Issa</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:10:16.850780+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Delivery of 47 Humvees and five trucks to the Lebanese Armed Forces</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>https://lb.usembassy.gov/delivery-of-47-humvees-and-five-trucks-to-the-lebanese-armed-forces/</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>We use cookies to make our website work better and improve your experience. By continuing to use the site, you agree to our privacy policy.
+The technical storage or access is strictly necessary for the legitimate purpose of enabling the use of a specific service explicitly requested by the subscriber or user, or for the sole purpose of carrying out the transmission of a communication over an electronic communications network.
+The technical storage or access is necessary for the legitimate purpose of storing preferences that are not requested by the subscriber or user.
+The technical storage or access that is used exclusively for statistical purposes.
+The technical storage or access that is used exclusively for anonymous statistical purposes. Without a subpoena, voluntary compliance on the part of your Internet Service Provider, or additional records from a third party, information stored or retrieved for this purpose alone cannot usually be used to identify you.
+The technical storage or access is required to create user profiles to send advertising, or to track the user on a website or across several websites for similar marketing purposes.</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:10:22.959959+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Secretary Rubio’s Meeting with Lebanese Prime Minister Salam</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>https://lb.usembassy.gov/secretary-rubios-meeting-with-lebanese-prime-minister-salam/</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>We use cookies to make our website work better and improve your experience. By continuing to use the site, you agree to our privacy policy.
+The technical storage or access is strictly necessary for the legitimate purpose of enabling the use of a specific service explicitly requested by the subscriber or user, or for the sole purpose of carrying out the transmission of a communication over an electronic communications network.
+The technical storage or access is necessary for the legitimate purpose of storing preferences that are not requested by the subscriber or user.
+The technical storage or access that is used exclusively for statistical purposes.
+The technical storage or access that is used exclusively for anonymous statistical purposes. Without a subpoena, voluntary compliance on the part of your Internet Service Provider, or additional records from a third party, information stored or retrieved for this purpose alone cannot usually be used to identify you.
+The technical storage or access is required to create user profiles to send advertising, or to track the user on a website or across several websites for similar marketing purposes.</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:10:29.958912+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Remarks by Ambassador Issa at the 40th Annual American Task Force on Lebanon Dinner</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>https://lb.usembassy.gov/remarks-by-ambassador-issa-at-the-40th-annual-american-task-force-on-lebanon-dinner/</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>If you remember only one sentence from me tonight, remember this. Lebanon’s moment has come and this time we must not let it pass.
+Less than one year ago, I began serving as United States Ambassador to Lebanon. Over these past months, I have witnessed serious challenges, but I have also witnessed something Lebanon has not experienced in a very long time, a genuine opportunity for change. I say this as the ambassador, as the American ambassador, but I also say it as someone who was born in Beirut, who understands Lebanon’s people and who knows both their extraordinary strengths and the heavy price they have paid.
+When I arrived in Lebanon, state’s institutions were being weakened. Too many families had lost their savings. Too many young people had lost hope. And too many of Lebanon’s most talented citizens believed that their only future was somewhere else. Lebanon was also trapped in a cycle of conflict with Israel, with no meaningful political process between the two governments and no credible path toward resolving the issue separating them.
+Today, that situation is beginning to change. In only a few months we have advanced negotiations between Lebanon and Israel further than many believed possible. We have brought the two governments into serious discussions after decades of hostility, mistrust, and conflict. While we do not yet have a final agreement, confidence-building steps have been achieved. Difficult issues have been addressed through diplomacy instead of being left entirely to the battlefield. That is real progress, and we should recognize it. Our objective is clear: a sovereign Lebanon, secure within its borders, and an Israel that is secure from attack across those borders. These are not competing goals. Lasting peace requires both of them.
+This progress did not happen by accident. It required the decisive leadership of President Donald Trump, the strong support and influence of Vice President Vance, and the diplomatic leadership of Secretary of State Marco Rubio. Their leadership gave us the credibility, determination, and political support necessary to move these discussions forward. President Trump understands that peace is achieved through strength, clarity, and the courage to challenge assumptions that have kept conflict frozen for generations. He has made clear that the United States is prepared to lead, to engage, and to pursue results. Vice President Vance and Secretary Rubio have also played critical roles in maintaining America’s support at the highest levels of our government. I have seen firsthand how American leadership can change the calculation. It can open doors that were closed. It can bring people to the table, and it can turn what once seemed impossible into something achievable. Credit, must also go to the leaders of Lebanon and Israel, who have been willing to engage in this process.
+Dialogue does not require the parties to agree on everything. It requires the courage to begin addressing what divides them. But diplomacy alone will not be enough. Lebanon cannot be sovereign in theory while remaining divided in practice.
+No political party or armed organization can be permitted to make decisions of war or peace outside the authority of the Lebanese state. The Lebanese armed forces and the legitimate institutions of the state must become the sole guarantors of Lebanon’s security throughout its territory. For too long, Iranian influence and Hizballah’s weapons have placed outside interests ahead of Lebanon national interests. This system weakened the state, paralyzed institutions, isolated Lebanon from its friends, and contributed to a collapse, whose cost was paid by ordinary Lebanese families.
+Moving Lebanon away from Iranian influence is not directed against any Lebanese community. It is for every Lebanese community. It is about building one country under one flag, protected by one national army, and governed by institutions that answer only to the Lebanese people.
+This brings me to all of you. The Lebanese American community, and the wider Lebanese diaspora. You have a central role to play. The Lebanese diaspora has always been one of Lebanon’s greatest strengths. You have succeeded in business, medicine, education, public service, technology, and nearly every profession. You have supported families, built institutions, created opportunities, and kept Lebanon connected to the world during its most difficult periods.
+But Lebanon now needs more than your affection. It needs your participation. Lebanon needs your investment, but it also needs your insistence on reform, transparency, and accountability. It needs your knowledge, your professional experience, your mentorship, your connections, and your confidence in what the country can become. Support entrepreneurs who want to build legitimate businesses. Mentor young Lebanese who are deciding whether they still have a future in their country. Help rebuild education, health care, energy, technology and the rule of law. Use your influence here in the United States to maintain strong American support for Lebanon’s legitimate institutions and for the Lebanese people. But do not let Lebanon’s next generation rebuild the same system that failed their parents. Help them build something better.
+America will continue to do its part. We will support Lebanon’s legitimate institutions. We will the Lebanese armed forces. We will encourage responsible investment and economic reform. And we will continue working to advance negotiation and to produce security, stability, and ultimately, peace. But Lebanon’s future will not be written in Washington, Tehran, or any other foreign capital. It will be written by Lebanese hands, and the hands of the Lebanese diaspora are part of that future.
+I remain hopeful because I have seen what becomes possible when America provides leadership, when Lebanon institutions assume responsibility, and when people refuse to accept that yesterday’s failure must not define tomorrow.
+We have an opportunity today that Lebanon may not have again for a very, very long time. We must continue the negotiations. We must strengthen the state. We must restore sovereignty, and we must give the next generation a Lebanese a reason to remain, a reason to return, and a reason to believe.
+So, I will end where I began. Lebanon’s moment has come, and we must not let it pass. Together let’s make a new future possible.
+I want to thank ATFL leadership: Its members and all of you for your longstanding commitment to the relationship between United States and Lebanon. I also want to recognize Ambassador Nada [Mouawad], who is here with us tonight.
+Nada, thank you for your service, your friendship, and your continued commitment to strengthening the relationship between our two countries.
+Thank you.
+God bless the United States of America, and God bless Lebanon.
+###</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:10:36.929996+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>U.S. Embassy Honors Six U.S. Government Exchange Alumni</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>https://lb.usembassy.gov/u-s-embassy-honors-six-u-s-government-exchange-alumni/</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>Over 130 alumni gathered to celebrate their U.S. exchange experiences; six local alumni were recognized for their positive impact and in strengthening U.S.-Lebanese ties over the past year.
+Last week, Ambassador Michel Issa hosted his first reception for participants of U.S. Government-sponsored exchange programs. Over 130 alumni from a wide range of programs, professions, and sectors, representing Lebanon’s rich human capital, joined the event. In addition to providing an opportunity to reconnect with old friends and make new connections, the evening celebrated the contributions of the following six alumni for using their U.S. exchange experiences to make a positive impact over the past year through leadership, community engagement, celebration of American excellence, and advocacy for U.S.-Lebanon cooperation:
+- Mr. Amir Hijazi, co-founder and Executive Board Member of the MAAN Initiative (Kennedy-Lugar Youth Exchange and Study (YES) Program, 2007, and Community Engagement Exchange Program, 2024)
+- Mr. Francesco Bakhos, Project Manager at SmartESA (Fulbright Masters Program, 2022)
+- Ms. Kholoud El Gharib, Program Coordinator at the American Corner Beirut (English Access Scholarship Program, 2009)
+- Dr. Maria Bassil, Professor of Physics at the Lebanese University (Fulbright Visiting Scholar Program, 2011)
+- Ms. Rawan Yaghi, Founder of USPEaK (Hubert H. Humphrey Fellowship, 2014)
+- Dr. Ziad El Sayegh, Executive Director of the Civic Influence Hub (International Visitor Leadership Program, 2018)
+In his remarks, Ambassador Issa praised the alumni for serving as “A bridge between our two countries and peoples that can promote stronger and deeper U.S.-Lebanese ties and advance our shared goals, including peace.”
+The Ambassador also highlighted the role U.S. exchange alumni can play in shaping Lebanon’s future, “I’ve said this in almost every meeting since arriving in Beirut: Lebanon’s future will not be written in a foreign embassy. It will be written by Lebanese hands — by a sovereign
+state, strong, reformed-focused Lebanese institutions and leaders like you who refuse to let this country’s story end in someone else’s footnote.”
+Over the past fifty years, roughly 21,000 Lebanese have participated in U.S. government-funded exchange, educational, and cultural programs, including the prestigious U.S. Fulbright, Humphrey, International Visitor Leadership, and Middle East Partnership Initiative (MEPI) programs. While many travelled to the United States for a fixed program of study, research, or professional development and some lived with American host families or on U.S. university campuses, over 8,000 Lebanese youth, between 13-18 years, from across the country participated in the Lebanon-based U.S. Department of State-sponsored English Access program. In addition, over 3,300 of Lebanon’s brightest students have pursued studies at the world-class American University of Beirut and Lebanese American University through the MEPI’s Tomorrow’s Leaders and Higher Education Scholarship programs, as well as other MEPI-sponsored academic and leadership programs whose alumni were also present at the reception. Through all the exchanges, participants shared Lebanese culture and history and participated in U.S. cultural activities, helping to deepen and expand mutual understanding and respect, building on the two centuries of friendship between the American and the Lebanese people.
+For more information about U.S. Government exchange programs and to learn about current programs accepting applications, visit: https://lb.usembassy.gov/education/ and https://lb.usembassy.gov/the-fulbright-visiting-scholar-program-2027-2028/
+Follow the Embassy’s social media accounts on Facebook, Instagram, X, and YouTube: @USEmbassyBeirut</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:10:38.672782+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Ambassador Michel Issa Visits Southern Lebanon</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>https://lb.usembassy.gov/ambassador-michel-issa-visits-southern-lebanon/</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>U.S. Ambassador Michel Issa visited southern Lebanon today to assess conditions on the ground and see firsthand the progress and challenges in the pilot zones. The United States remains committed to supporting the Government of Lebanon and the Lebanese Armed Forces in strengthening state authority, protecting civilians, providing services, and creating conditions that help bring about lasting peace and stability.
+We will continue to work with all relevant parties to support a more secure and stable southern Lebanon.
+The Ambassador said “My visit to southern Lebanon allowed me to witness firsthand the challenges facing its communities. I deeply sympathize with residents who have endured displacement and uncertainty, and I understand their urgent desire to return home and rebuild their lives in safety and dignity.”</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:10:45.528613+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>The FBI’s Art Crime Team Returns Archaeological Artifacts to the Government of Lebanon</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>https://lb.usembassy.gov/the-fbis-art-crime-team-returns-archaeological-artifacts-to-the-government-of-lebanon/</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>We use cookies to make our website work better and improve your experience. By continuing to use the site, you agree to our privacy policy.
+The technical storage or access is strictly necessary for the legitimate purpose of enabling the use of a specific service explicitly requested by the subscriber or user, or for the sole purpose of carrying out the transmission of a communication over an electronic communications network.
+The technical storage or access is necessary for the legitimate purpose of storing preferences that are not requested by the subscriber or user.
+The technical storage or access that is used exclusively for statistical purposes.
+The technical storage or access that is used exclusively for anonymous statistical purposes. Without a subpoena, voluntary compliance on the part of your Internet Service Provider, or additional records from a third party, information stored or retrieved for this purpose alone cannot usually be used to identify you.
+The technical storage or access is required to create user profiles to send advertising, or to track the user on a website or across several websites for similar marketing purposes.</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:10:51.651014+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Statement from Ambassador Issa</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>https://lb.usembassy.gov/statement-from-ambassador-issa/</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>We use cookies to make our website work better and improve your experience. By continuing to use the site, you agree to our privacy policy.
+The technical storage or access is strictly necessary for the legitimate purpose of enabling the use of a specific service explicitly requested by the subscriber or user, or for the sole purpose of carrying out the transmission of a communication over an electronic communications network.
+The technical storage or access is necessary for the legitimate purpose of storing preferences that are not requested by the subscriber or user.
+The technical storage or access that is used exclusively for statistical purposes.
+The technical storage or access that is used exclusively for anonymous statistical purposes. Without a subpoena, voluntary compliance on the part of your Internet Service Provider, or additional records from a third party, information stored or retrieved for this purpose alone cannot usually be used to identify you.
+The technical storage or access is required to create user profiles to send advertising, or to track the user on a website or across several websites for similar marketing purposes.</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:11:01.632430+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>President Trump Participates in a Bilateral Meeting with the President of the Republic of Lebanon</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>https://lb.usembassy.gov/president-trump-participates-in-a-bilateral-meeting-with-the-president-of-the-republic-of-lebanon/</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>President Trump Participates in a Bilateral Meeting with the President of the Republic of Lebanon
+POTUS meets with Lebanese President Joseph Aoun
+We use cookies to make our website work better and improve your experience. By continuing to use the site, you agree to our privacy policy.
+An official website of the United States government
+Official websites use .gov
+A .gov website belongs to an official government organization in the United States.
+Secure .gov websites use HTTPS
+A lock (
+) or https:// means you’ve safely connected to the .gov website. Share sensitive information only on official, secure websites.
+Worldwide Caution: The Department of State advises Americans worldwide to exercise increased caution.
+U.S. Citizens with emergencies, please send an e-mail to BeirutACS@state.gov
+If you have reasons to believe that you or any of your family members are in danger, please contact the local Internal Security Forces at 112
+Emergency Contact – All Locations Get Travel Alerts International Parental Child Abduction Arrest of a U.S. Citizen Death of a U.S. Citizen Victims of Crime Emergency Financial Assistance</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>2026-10-29T12:11:08.884051+00:00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
